--- a/PCB/Project Outputs for Twintig-Tap-Pads/BOM/Bill of Materials-Twintig-Tap-Pads.xlsx
+++ b/PCB/Project Outputs for Twintig-Tap-Pads/BOM/Bill of Materials-Twintig-Tap-Pads.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-Tap-Pads\PCB\Project Outputs for Twintig-Tap-Pads\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{044D5517-7CD5-4ECD-8B04-A3198F3F6D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96097E40-E874-4D6D-9BB5-ACCD6C63773C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15370" xr2:uid="{E937C1E9-8460-426E-B519-72266238BE25}"/>
+    <workbookView xWindow="-25370" yWindow="380" windowWidth="24830" windowHeight="21220" xr2:uid="{AB15F0BC-A282-47DF-B6C6-38D23F1C0CCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-Tap-P" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t>Designator</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Footprint</t>
   </si>
   <si>
-    <t>C1, C2, C3, C5, C6, C7, C8, C11, C12, C13, C14, C15, C16, C17, C18, C19</t>
+    <t>C1, C2, C3, C5, C6, C7, C8, C9, C20</t>
   </si>
   <si>
     <t>100nF</t>
@@ -60,13 +60,19 @@
     <t>Capacitor 0402</t>
   </si>
   <si>
-    <t>C4, C9, C10</t>
+    <t>C4, C10, C11</t>
   </si>
   <si>
     <t>10uF</t>
   </si>
   <si>
-    <t>C20, C21, C22, C23, C24, C25, C26, C27</t>
+    <t>C12, C13, C14, C15, C16, C17, C18, C19</t>
+  </si>
+  <si>
+    <t>220pF</t>
+  </si>
+  <si>
+    <t>C21, C22, C23, C24, C25, C26, C27, C28</t>
   </si>
   <si>
     <t>Capacitor 0603</t>
@@ -96,46 +102,58 @@
     <t>Molex 217179-0001</t>
   </si>
   <si>
-    <t>J3, J4, J5, J6, J7, J8, J9, J10</t>
-  </si>
-  <si>
-    <t>Wire Solder Pad</t>
-  </si>
-  <si>
-    <t>Wire Solder Pad 3x1.5mm</t>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>Molex 90121-0766</t>
+  </si>
+  <si>
+    <t>Molex 90120-0926</t>
+  </si>
+  <si>
+    <t>J4, J5, J6, J7</t>
+  </si>
+  <si>
+    <t>Molex 90121-0763</t>
   </si>
   <si>
     <t>R1</t>
   </si>
   <si>
+    <t>10kR</t>
+  </si>
+  <si>
+    <t>Resistor 0402</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
     <t>33R</t>
   </si>
   <si>
-    <t>Resistor 0402</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>10kR</t>
-  </si>
-  <si>
     <t>R3, R4</t>
   </si>
   <si>
     <t>5.1kR</t>
   </si>
   <si>
-    <t>R5, R8, R11, R14</t>
+    <t>R5, R6, R7, R8</t>
+  </si>
+  <si>
+    <t>470R</t>
+  </si>
+  <si>
+    <t>R9, R12, R15, R18</t>
   </si>
   <si>
     <t>Interlink FSR 406</t>
   </si>
   <si>
-    <t>R6, R7, R9, R10, R12, R13, R15, R16</t>
-  </si>
-  <si>
-    <t>1kR</t>
+    <t>R10, R11, R13, R14, R16, R17, R19, R20</t>
+  </si>
+  <si>
+    <t>100kR</t>
   </si>
   <si>
     <t>U1</t>
@@ -556,8 +574,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BA42557-3195-405E-922D-848121ABDBDE}">
-  <dimension ref="A1:D18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{898600BD-6FAE-4740-9FCE-F6A5C1EECED1}">
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="87.81640625" customWidth="1"/>
@@ -585,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -616,10 +634,10 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -627,38 +645,38 @@
         <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
@@ -669,55 +687,55 @@
         <v>19</v>
       </c>
       <c r="B8" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="1">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -725,13 +743,13 @@
         <v>29</v>
       </c>
       <c r="B12" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -739,13 +757,13 @@
         <v>31</v>
       </c>
       <c r="B13" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -753,69 +771,111 @@
         <v>33</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="1">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/PCB/Project Outputs for Twintig-Tap-Pads/BOM/Bill of Materials-Twintig-Tap-Pads.xlsx
+++ b/PCB/Project Outputs for Twintig-Tap-Pads/BOM/Bill of Materials-Twintig-Tap-Pads.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-Tap-Pads\PCB\Project Outputs for Twintig-Tap-Pads\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96097E40-E874-4D6D-9BB5-ACCD6C63773C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F913363-691E-4D24-ABFF-7A209B7864D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25370" yWindow="380" windowWidth="24830" windowHeight="21220" xr2:uid="{AB15F0BC-A282-47DF-B6C6-38D23F1C0CCF}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="24686" windowHeight="14597" xr2:uid="{926921F2-7270-42FB-A754-04083358450F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-Tap-P" sheetId="1" r:id="rId1"/>
@@ -574,17 +574,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{898600BD-6FAE-4740-9FCE-F6A5C1EECED1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625FDE27-51BE-4CD4-BDF3-D46621917BEB}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="87.81640625" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" customWidth="1"/>
-    <col min="3" max="3" width="25.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
+    <col min="1" max="1" width="86.61328125" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="25.07421875" customWidth="1"/>
+    <col min="4" max="4" width="24.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -598,7 +598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -612,7 +612,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -626,7 +626,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -640,7 +640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -654,7 +654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -668,7 +668,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -682,7 +682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -696,7 +696,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -710,7 +710,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -724,7 +724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -738,7 +738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -752,7 +752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
@@ -766,7 +766,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
@@ -780,7 +780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
@@ -794,7 +794,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
@@ -808,7 +808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>39</v>
       </c>
@@ -822,7 +822,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>42</v>
       </c>
@@ -836,7 +836,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
@@ -850,7 +850,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>48</v>
       </c>
@@ -864,7 +864,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>51</v>
       </c>

--- a/PCB/Project Outputs for Twintig-Tap-Pads/BOM/Bill of Materials-Twintig-Tap-Pads.xlsx
+++ b/PCB/Project Outputs for Twintig-Tap-Pads/BOM/Bill of Materials-Twintig-Tap-Pads.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-Tap-Pads\PCB\Project Outputs for Twintig-Tap-Pads\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F913363-691E-4D24-ABFF-7A209B7864D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C82FFAE4-4350-4BCC-B66D-3838D98B7B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="24686" windowHeight="14597" xr2:uid="{926921F2-7270-42FB-A754-04083358450F}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="24686" windowHeight="14597" xr2:uid="{1CF3CD1F-9299-41AF-BE99-CB2A4D064DAE}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-Tap-P" sheetId="1" r:id="rId1"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625FDE27-51BE-4CD4-BDF3-D46621917BEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A67A8D2-FD10-458D-81EE-44402CB3320E}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>

--- a/PCB/Project Outputs for Twintig-Tap-Pads/BOM/Bill of Materials-Twintig-Tap-Pads.xlsx
+++ b/PCB/Project Outputs for Twintig-Tap-Pads/BOM/Bill of Materials-Twintig-Tap-Pads.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-Tap-Pads\PCB\Project Outputs for Twintig-Tap-Pads\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C82FFAE4-4350-4BCC-B66D-3838D98B7B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D49499C-BEEE-4B7E-AFC1-CBBA967FFA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="24686" windowHeight="14597" xr2:uid="{1CF3CD1F-9299-41AF-BE99-CB2A4D064DAE}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="24686" windowHeight="14597" xr2:uid="{40BF0153-62FB-40CC-8091-8BD6BC90C2A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-Tap-P" sheetId="1" r:id="rId1"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A67A8D2-FD10-458D-81EE-44402CB3320E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1152E5-65C6-4AE6-9E07-A40C681C7108}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
